--- a/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>고유id (동료id_레벨)</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>Id</t>
@@ -552,13 +555,13 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -566,33 +569,33 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3">
         <v>1.0</v>
@@ -612,10 +615,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -635,10 +638,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3">
         <v>3.0</v>
@@ -658,10 +661,10 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4">
         <v>4.0</v>
@@ -681,10 +684,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4">
         <v>5.0</v>
@@ -704,10 +707,10 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4">
         <v>6.0</v>
@@ -727,10 +730,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4">
         <v>7.0</v>
@@ -750,10 +753,10 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4">
         <v>8.0</v>
@@ -773,10 +776,10 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4">
         <v>9.0</v>
@@ -796,10 +799,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4">
         <v>10.0</v>
@@ -819,10 +822,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3">
         <v>1.0</v>
@@ -842,10 +845,10 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C15" s="3">
         <v>2.0</v>
@@ -865,10 +868,10 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="4">
         <v>3.0</v>
@@ -888,10 +891,10 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4">
         <v>4.0</v>
@@ -911,10 +914,10 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4">
         <v>5.0</v>
@@ -934,10 +937,10 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="4">
         <v>6.0</v>
@@ -957,10 +960,10 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="4">
         <v>7.0</v>
@@ -980,10 +983,10 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="4">
         <v>8.0</v>
@@ -1003,10 +1006,10 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="4">
         <v>9.0</v>
@@ -1026,10 +1029,10 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="4">
         <v>10.0</v>
@@ -1049,10 +1052,10 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" s="4">
         <v>1.0</v>
@@ -1072,10 +1075,10 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="C25" s="4">
         <v>2.0</v>
@@ -1095,10 +1098,10 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="4">
         <v>3.0</v>
@@ -1118,10 +1121,10 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" s="4">
         <v>4.0</v>
@@ -1141,10 +1144,10 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="4">
         <v>5.0</v>
@@ -1164,10 +1167,10 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="4">
         <v>6.0</v>
@@ -1187,10 +1190,10 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4">
         <v>7.0</v>
@@ -1210,10 +1213,10 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C31" s="4">
         <v>8.0</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" s="4">
         <v>9.0</v>
@@ -1256,10 +1259,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2">
         <v>10.0</v>
@@ -1279,10 +1282,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3">
         <v>1.0</v>
@@ -1302,10 +1305,10 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="C35" s="4">
         <v>2.0</v>
@@ -1325,10 +1328,10 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C36" s="4">
         <v>3.0</v>
@@ -1348,10 +1351,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="4">
         <v>4.0</v>
@@ -1371,10 +1374,10 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" s="4">
         <v>5.0</v>
@@ -1394,10 +1397,10 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" s="4">
         <v>6.0</v>
@@ -1417,10 +1420,10 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="4">
         <v>7.0</v>
@@ -1440,10 +1443,10 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4">
         <v>8.0</v>
@@ -1463,10 +1466,10 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4">
         <v>9.0</v>
@@ -1486,10 +1489,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" s="3">
         <v>10.0</v>
@@ -1509,10 +1512,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" s="3">
         <v>1.0</v>
@@ -1532,10 +1535,10 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="C45" s="4">
         <v>2.0</v>
@@ -1555,10 +1558,10 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C46" s="4">
         <v>3.0</v>
@@ -1578,10 +1581,10 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" s="4">
         <v>4.0</v>
@@ -1601,10 +1604,10 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" s="4">
         <v>5.0</v>
@@ -1624,10 +1627,10 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C49" s="4">
         <v>6.0</v>
@@ -1647,10 +1650,10 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C50" s="4">
         <v>7.0</v>
@@ -1670,10 +1673,10 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51" s="4">
         <v>8.0</v>
@@ -1693,10 +1696,10 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C52" s="4">
         <v>9.0</v>
@@ -1716,10 +1719,10 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C53" s="4">
         <v>10.0</v>

--- a/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
@@ -55,10 +55,10 @@
     <t>HP</t>
   </si>
   <si>
-    <t>ATK</t>
-  </si>
-  <si>
-    <t>DEF</t>
+    <t>BaseAttack</t>
+  </si>
+  <si>
+    <t>BaseDefense</t>
   </si>
   <si>
     <t>UpgradeCost</t>
@@ -258,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,6 +277,12 @@
         <bgColor rgb="FFFDFDFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -284,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -292,6 +298,9 @@
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -580,10 +589,10 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -591,669 +600,669 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>100.0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>10.0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>2.0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>112.0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>11.0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>11.0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>10.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>3.0</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>125.0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>12.0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>12.0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>15.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>4.0</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>140.0</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>13.0</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>13.0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>20.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>5.0</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>157.0</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>15.0</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>14.0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>30.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>6.0</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>176.0</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>16.0</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>15.0</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>40.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>7.0</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>197.0</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>18.0</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>16.0</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>55.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>8.0</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>221.0</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>19.0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>17.0</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>75.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>9.0</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>248.0</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>21.0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>19.0</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>100.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>10.0</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>277.0</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>24.0</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>20.0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>140.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>1.0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>80.0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <v>13.0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>8.0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>2.0</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>90.0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <v>14.0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>9.0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <v>10.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>3.0</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>100.0</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>16.0</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>9.0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>15.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>4.0</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>112.0</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>17.0</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <v>10.0</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <v>20.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>5.0</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>126.0</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>19.0</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>11.0</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>30.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>6.0</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>141.0</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>21.0</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <v>12.0</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <v>40.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>7.0</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>158.0</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>23.0</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>13.0</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <v>55.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>8.0</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>177.0</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>25.0</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <v>14.0</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="5">
         <v>75.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>9.0</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>198.0</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>28.0</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="5">
         <v>15.0</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="5">
         <v>100.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>10.0</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>222.0</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>31.0</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>16.0</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <v>140.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>1.0</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>110.0</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>14.0</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
         <v>10.0</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>2.0</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>123.0</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>15.0</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <v>11.0</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="5">
         <v>10.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>3.0</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>138.0</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>17.0</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="5">
         <v>12.0</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="5">
         <v>15.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>4.0</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>155.0</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>19.0</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <v>13.0</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <v>20.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>5.0</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>173.0</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>20.0</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="5">
         <v>14.0</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="5">
         <v>30.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>6.0</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>194.0</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>23.0</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="5">
         <v>15.0</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="5">
         <v>40.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>7.0</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>217.0</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>25.0</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>16.0</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>55.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>8.0</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>243.0</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>27.0</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>17.0</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="5">
         <v>75.0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>9.0</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>272.0</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>30.0</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <v>19.0</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="5">
         <v>100.0</v>
       </c>
     </row>
@@ -1281,462 +1290,462 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="4">
         <v>1.0</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <v>115.0</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="4">
         <v>15.0</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <v>15.0</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>2.0</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>129.0</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="5">
         <v>17.0</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="5">
         <v>16.0</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="5">
         <v>10.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>3.0</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="5">
         <v>144.0</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="5">
         <v>18.0</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="5">
         <v>17.0</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="5">
         <v>15.0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="5">
         <v>4.0</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="5">
         <v>162.0</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <v>20.0</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="5">
         <v>19.0</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="5">
         <v>20.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="5">
         <v>5.0</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="5">
         <v>181.0</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="5">
         <v>22.0</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="5">
         <v>20.0</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="5">
         <v>30.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <v>6.0</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="5">
         <v>203.0</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="5">
         <v>24.0</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="5">
         <v>22.0</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="5">
         <v>40.0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <v>7.0</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="5">
         <v>227.0</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="5">
         <v>27.0</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="5">
         <v>24.0</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="5">
         <v>55.0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>8.0</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>254.0</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="5">
         <v>29.0</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="5">
         <v>26.0</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="5">
         <v>75.0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <v>9.0</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="5">
         <v>285.0</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="5">
         <v>32.0</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="5">
         <v>28.0</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="5">
         <v>100.0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="4">
         <v>10.0</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="4">
         <v>319.0</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="4">
         <v>35.0</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="4">
         <v>30.0</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="4">
         <v>140.0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="4">
         <v>1.0</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="4">
         <v>120.0</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="4">
         <v>15.0</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="4">
         <v>16.0</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <v>2.0</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="5">
         <v>134.0</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="5">
         <v>17.0</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="5">
         <v>17.0</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="5">
         <v>10.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <v>3.0</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="5">
         <v>151.0</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="5">
         <v>18.0</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="5">
         <v>19.0</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="5">
         <v>15.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>4.0</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="5">
         <v>169.0</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="5">
         <v>20.0</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="5">
         <v>20.0</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47" s="5">
         <v>20.0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>5.0</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="5">
         <v>189.0</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="5">
         <v>22.0</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="5">
         <v>22.0</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48" s="5">
         <v>30.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <v>6.0</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="5">
         <v>211.0</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="5">
         <v>24.0</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="5">
         <v>24.0</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49" s="5">
         <v>40.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="5">
         <v>7.0</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="5">
         <v>237.0</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="5">
         <v>27.0</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="5">
         <v>25.0</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="5">
         <v>55.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="5">
         <v>8.0</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>265.0</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="5">
         <v>29.0</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="5">
         <v>27.0</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="5">
         <v>75.0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>9.0</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="5">
         <v>297.0</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="5">
         <v>32.0</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="5">
         <v>30.0</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="5">
         <v>100.0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>10.0</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="5">
         <v>333.0</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="5">
         <v>35.0</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="5">
         <v>32.0</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53" s="5">
         <v>140.0</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionLevelData.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -145,6 +145,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -410,7 +413,7 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="3">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="5" ht="24.0" customHeight="1">
@@ -421,7 +424,7 @@
         <v>2.0</v>
       </c>
       <c r="C5" s="3">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="6" ht="24.0" customHeight="1">
@@ -432,7 +435,7 @@
         <v>3.0</v>
       </c>
       <c r="C6" s="3">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="7" ht="24.0" customHeight="1">
@@ -443,7 +446,7 @@
         <v>4.0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="8" ht="24.0" customHeight="1">
@@ -454,7 +457,7 @@
         <v>5.0</v>
       </c>
       <c r="C8" s="3">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="9" ht="24.0" customHeight="1">
@@ -465,7 +468,7 @@
         <v>6.0</v>
       </c>
       <c r="C9" s="3">
-        <v>40.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="10" ht="24.0" customHeight="1">
@@ -476,7 +479,7 @@
         <v>7.0</v>
       </c>
       <c r="C10" s="3">
-        <v>55.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="11" ht="24.0" customHeight="1">
@@ -487,7 +490,7 @@
         <v>8.0</v>
       </c>
       <c r="C11" s="3">
-        <v>75.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="12" ht="24.0" customHeight="1">
@@ -498,7 +501,7 @@
         <v>9.0</v>
       </c>
       <c r="C12" s="3">
-        <v>100.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="13" ht="24.0" customHeight="1">
@@ -508,8 +511,8 @@
       <c r="B13" s="3">
         <v>10.0</v>
       </c>
-      <c r="C13" s="3">
-        <v>140.0</v>
+      <c r="C13" s="5">
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
